--- a/implementation assets/translations.xlsx
+++ b/implementation assets/translations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joel.miller\Documents\Development\New Digital Kiosk\implementation assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC63094C-1838-4AFC-AFE9-14579FC6F631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBDD9DD3-072A-4D1C-99C0-A2A97260E4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18660" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{1CB09CF4-96A6-46EC-9721-80AE60DC6C68}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1CB09CF4-96A6-46EC-9721-80AE60DC6C68}"/>
   </bookViews>
   <sheets>
     <sheet name="Flyer Translations (Proofed)" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>使用 Shopper Portal，退税购物更轻松</t>
   </si>
@@ -99,13 +99,34 @@
   </si>
   <si>
     <t>Subheading</t>
+  </si>
+  <si>
+    <t>Screen preservation text</t>
+  </si>
+  <si>
+    <t>Obtenga su Reembolso Tax Free aquí</t>
+  </si>
+  <si>
+    <t>轻松领取您的退税</t>
+  </si>
+  <si>
+    <t>احصل على استرداد الضريبة هنا</t>
+  </si>
+  <si>
+    <t>Obtenez votre remboursement de détaxe ici</t>
+  </si>
+  <si>
+    <t>Obtenha o seu reembolso Tax Free aqui</t>
+  </si>
+  <si>
+    <t>Claim your Tax Free refund</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
@@ -148,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -166,6 +187,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -500,8 +522,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E579F357-8044-4B4E-9D83-4201C0E59C55}">
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="24.54296875" customWidth="1"/>
     <col min="2" max="2" width="43.453125" bestFit="1" customWidth="1"/>
@@ -512,7 +534,7 @@
     <col min="7" max="7" width="36.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
@@ -535,7 +557,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -558,7 +580,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -579,6 +601,29 @@
       </c>
       <c r="G3" s="1" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
